--- a/data/trans_orig/IP22D2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22D2_2023-Edad-trans_orig.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>72,63%</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15382</t>
+          <t>15490</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>23412</t>
+          <t>23620</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>90,06%</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>19287</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>9597</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26924</t>
+          <t>26539</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,06%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18219</t>
+          <t>18471</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14738</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13247</t>
+          <t>13413</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30521</t>
+          <t>30863</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31383</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29465</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33880</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>56130</t>
+          <t>54485</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>54,01%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33312</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35721</t>
+          <t>35465</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43246</t>
+          <t>44136</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64581</t>
+          <t>65998</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22D2_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4695</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>87,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>51,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6161</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3418</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>87,99%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>48,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5479</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3411</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6151</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>89,07%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>55,45%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5537</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3344</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6261</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>88,44%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>53,4%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>21</t>
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>644</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>672</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,15%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5339</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4424</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2066</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7582</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>42,13%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>19,67%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>72,2%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3957</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1702</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>6370</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>49,1%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>21,12%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>79,04%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13265</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>60,85%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5627</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2840</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8141</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>53,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>77,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4102</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1689</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6357</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>50,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>78,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>74,03%</t>
         </is>
       </c>
     </row>
@@ -1628,107 +1628,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>23,01%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8059</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,107 +1858,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>30,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>53,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4972</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>8877</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>29,74%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>53,1%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9616</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5847</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>12821</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>63,6%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>38,68%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>84,8%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>10130</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>10821</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>6539</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>14091</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>64,72%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>19747</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>23620</t>
+          <t>22556</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,33%</t>
         </is>
       </c>
     </row>
@@ -2084,107 +2084,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4057</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5495</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4796</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>15119</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6022</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2122</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>11048</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>35,5%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>65,13%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>10214</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>4379</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>19287</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>43,28%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>18,56%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>81,73%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>16553</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26539</t>
+          <t>18057</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>49,23%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10940</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5914</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14840</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>64,5%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>34,87%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>87,49%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>12729</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3996</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>18471</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>53,94%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>16,93%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>78,28%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>13280</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14738</t>
+          <t>16403</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>23586</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>18396</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>29220</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>79,66%</t>
         </is>
       </c>
     </row>
@@ -2766,107 +2766,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3599</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3664</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>18,58%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3698</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>16962</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>16962</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>16962</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>23598</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>40794</t>
+          <t>36683</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40794</t>
+          <t>36683</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40794</t>
+          <t>36683</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>19700</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>14017</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>26402</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>29,25%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>55,09%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>20332</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>13515</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>30398</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>42,21%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>28,06%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>63,11%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22327</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16131</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29506</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>42659</t>
+          <t>34060</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>25358</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54485</t>
+          <t>42497</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>26827</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>19354</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>32518</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>55,98%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>40,39%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>67,86%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>27179</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>16782</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>33783</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>56,43%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>34,84%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>70,14%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>28053</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>22722</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>56121</t>
+          <t>54879</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44136</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65998</t>
+          <t>63492</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>69,81%</t>
         </is>
       </c>
     </row>
@@ -3222,107 +3222,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4748</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>5218</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>4832</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>618</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>100879</t>
+          <t>90952</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>100879</t>
+          <t>90952</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100879</t>
+          <t>90952</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
